--- a/output/walk_forward_reports/parameter_sensitivity.xlsx
+++ b/output/walk_forward_reports/parameter_sensitivity.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\walk_forward_reports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99081FEB-EC4D-4D49-98F7-E82D7EB2B67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="group_num" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,7 @@
     <sheet name="rebalance_period" sheetId="3" r:id="rId3"/>
     <sheet name="weight_method" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -58,13 +64,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -96,13 +109,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -140,7 +161,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -174,6 +195,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -208,9 +230,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -383,11 +406,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -401,33 +429,46 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5</v>
       </c>
+      <c r="B2">
+        <v>1.127364391005119</v>
+      </c>
+      <c r="C2">
+        <v>1.9599272929089959</v>
+      </c>
       <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>10</v>
       </c>
+      <c r="B3">
+        <v>1.0136759815240111</v>
+      </c>
+      <c r="C3">
+        <v>1.9951708038747049</v>
+      </c>
       <c r="D3">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -441,41 +482,64 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1.0527544808008089</v>
+      </c>
+      <c r="C2">
+        <v>1.8439664596395959</v>
+      </c>
       <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>0.95896557539277205</v>
+      </c>
+      <c r="C3">
+        <v>2.0173196299459262</v>
+      </c>
       <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1.199840502600114</v>
+      </c>
+      <c r="C4">
+        <v>2.0619348027575</v>
+      </c>
       <c r="D4">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.26953125" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -489,49 +553,77 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>10</v>
       </c>
+      <c r="B2">
+        <v>1.0123250728045809</v>
+      </c>
+      <c r="C2">
+        <v>1.7591881255713111</v>
+      </c>
       <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>20</v>
       </c>
+      <c r="B3">
+        <v>0.98635530674296645</v>
+      </c>
+      <c r="C3">
+        <v>1.9136472295595119</v>
+      </c>
       <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>30</v>
       </c>
+      <c r="B4">
+        <v>1.016421673694168</v>
+      </c>
+      <c r="C4">
+        <v>2.0469741386610631</v>
+      </c>
       <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>60</v>
       </c>
+      <c r="B5">
+        <v>1.2669786918165451</v>
+      </c>
+      <c r="C5">
+        <v>2.1632759774997541</v>
+      </c>
       <c r="D5">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -545,47 +637,78 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
+      <c r="B2">
+        <v>1.1964826906385519</v>
+      </c>
+      <c r="C2">
+        <v>1.905171827246541</v>
+      </c>
       <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
+      <c r="B3">
+        <v>1.1791937843468809</v>
+      </c>
+      <c r="C3">
+        <v>1.9638124892325179</v>
+      </c>
       <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
+      <c r="B4">
+        <v>0.93247388069222736</v>
+      </c>
+      <c r="C4">
+        <v>2.1141632157422712</v>
+      </c>
       <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
+      <c r="B5">
+        <v>0.92318630857318107</v>
+      </c>
+      <c r="C5">
+        <v>1.908680533347739</v>
+      </c>
       <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6">
+        <v>1.121264267071983</v>
+      </c>
+      <c r="C6">
+        <v>1.985421481050496</v>
+      </c>
       <c r="D6">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>